--- a/data/выпуск_продукции.xlsx
+++ b/data/выпуск_продукции.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\АН\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15D50BE-8926-459C-BC53-BFC9A9608352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="1548" windowWidth="16596" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="1548" windowWidth="16596" windowHeight="9420"/>
   </bookViews>
   <sheets>
     <sheet name="Выпуск" sheetId="1" r:id="rId1"/>
@@ -73,7 +67,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -440,7 +434,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -578,9 +572,15 @@
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="B10" s="3">
+        <v>2589</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3229</v>
+      </c>
+      <c r="D10" s="3">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
